--- a/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
+++ b/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T07:53:37+00:00</t>
+    <t>2026-09-21T09:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
+++ b/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.5</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:39:56+00:00</t>
+    <t>2026-10-09T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
+++ b/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:40:46+00:00</t>
+    <t>2026-10-09T10:49:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
+++ b/CodeSystem-LokalLegemiddelkatalogCodeSystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.7</t>
+    <t>1.1.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:49:44+00:00</t>
+    <t>2026-10-20T08:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
